--- a/data/trans_camb/IP19C01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 10,78</t>
+          <t>-18,06; 9,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 13,82</t>
+          <t>-15,34; 14,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 13,59</t>
+          <t>-13,07; 13,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 12,12</t>
+          <t>-16,12; 12,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 3,45</t>
+          <t>-25,71; 1,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 18,54</t>
+          <t>-3,89; 19,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 7,37</t>
+          <t>-12,2; 8,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 4,97</t>
+          <t>-16,7; 4,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 14,38</t>
+          <t>-3,75; 13,53</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 15,31</t>
+          <t>-22,5; 13,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 20,31</t>
+          <t>-19,49; 20,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 20,38</t>
+          <t>-15,82; 20,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 16,91</t>
+          <t>-18,41; 16,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 4,53</t>
+          <t>-30,66; 1,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 26,83</t>
+          <t>-4,35; 27,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 10,09</t>
+          <t>-15,32; 10,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 6,58</t>
+          <t>-20,61; 5,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 19,94</t>
+          <t>-4,77; 19,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 23,3</t>
+          <t>-7,66; 23,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 29,65</t>
+          <t>-1,33; 29,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 30,62</t>
+          <t>1,81; 31,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 24,64</t>
+          <t>-7,69; 24,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 25,62</t>
+          <t>-4,75; 27,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 34,76</t>
+          <t>6,53; 35,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 17,44</t>
+          <t>-3,26; 19,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 22,97</t>
+          <t>1,59; 23,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 28,49</t>
+          <t>8,18; 28,3</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 39,93</t>
+          <t>-10,65; 43,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 54,35</t>
+          <t>-1,48; 53,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 54,89</t>
+          <t>2,75; 57,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 43,94</t>
+          <t>-10,88; 44,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 45,72</t>
+          <t>-6,68; 47,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 63,93</t>
+          <t>8,65; 63,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 29,36</t>
+          <t>-4,57; 32,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 38,69</t>
+          <t>2,21; 39,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,22; 49,23</t>
+          <t>11,28; 48,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 24,95</t>
+          <t>-5,53; 26,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 27,57</t>
+          <t>-7,93; 26,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 26,49</t>
+          <t>-11,95; 25,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 15,54</t>
+          <t>-14,78; 16,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 26,46</t>
+          <t>-4,99; 25,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 12,0</t>
+          <t>-22,04; 12,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 16,76</t>
+          <t>-5,52; 15,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 22,1</t>
+          <t>-0,26; 20,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 13,39</t>
+          <t>-11,64; 14,3</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 43,61</t>
+          <t>-7,44; 48,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 49,41</t>
+          <t>-10,28; 45,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 46,22</t>
+          <t>-16,14; 45,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 23,84</t>
+          <t>-19,16; 25,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 42,33</t>
+          <t>-6,77; 39,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 17,79</t>
+          <t>-28,69; 18,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 26,47</t>
+          <t>-7,21; 23,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 35,18</t>
+          <t>-0,31; 33,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 20,61</t>
+          <t>-15,85; 22,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 10,01</t>
+          <t>-11,08; 9,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 9,02</t>
+          <t>-12,37; 8,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 22,69</t>
+          <t>3,18; 22,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 14,08</t>
+          <t>-6,37; 14,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 12,85</t>
+          <t>-7,54; 12,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 12,04</t>
+          <t>-10,36; 11,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 9,14</t>
+          <t>-4,82; 9,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 7,46</t>
+          <t>-5,93; 8,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 14,31</t>
+          <t>-0,03; 14,03</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 15,25</t>
+          <t>-14,21; 14,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 13,69</t>
+          <t>-16,03; 12,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 34,91</t>
+          <t>4,22; 34,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 20,61</t>
+          <t>-8,2; 21,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 18,38</t>
+          <t>-9,54; 18,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 17,43</t>
+          <t>-13,26; 17,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 13,37</t>
+          <t>-6,28; 13,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 10,66</t>
+          <t>-7,7; 11,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 20,44</t>
+          <t>0,11; 20,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 23,9</t>
+          <t>-5,25; 23,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 22,83</t>
+          <t>-6,76; 22,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,02; 37,99</t>
+          <t>6,41; 38,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 12,41</t>
+          <t>-14,68; 11,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 24,51</t>
+          <t>-0,49; 24,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,59; 32,12</t>
+          <t>7,57; 30,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 12,31</t>
+          <t>-6,65; 12,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 18,18</t>
+          <t>-0,09; 17,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,4; 30,57</t>
+          <t>11,06; 31,1</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 50,19</t>
+          <t>-7,83; 52,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 51,65</t>
+          <t>-10,06; 49,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11,38; 80,66</t>
+          <t>10,58; 83,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 20,08</t>
+          <t>-19,45; 18,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 40,77</t>
+          <t>-0,71; 39,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,39; 52,77</t>
+          <t>10,33; 51,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 21,34</t>
+          <t>-9,58; 20,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,09; 31,45</t>
+          <t>-0,1; 31,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18,72; 53,79</t>
+          <t>17,04; 55,3</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,53; 35,93</t>
+          <t>-0,23; 35,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 33,43</t>
+          <t>-5,12; 31,83</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,11; 39,97</t>
+          <t>8,98; 40,2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 19,45</t>
+          <t>-9,16; 20,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 7,29</t>
+          <t>-27,14; 7,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 23,1</t>
+          <t>-6,97; 21,84</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,09; 24,75</t>
+          <t>2,17; 24,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 16,93</t>
+          <t>-9,36; 16,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,28; 28,93</t>
+          <t>6,43; 28,21</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,69; 70,85</t>
+          <t>0,05; 73,13</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 68,66</t>
+          <t>-7,32; 62,08</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12,06; 82,14</t>
+          <t>12,91; 83,54</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 28,58</t>
+          <t>-10,67; 29,44</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 10,69</t>
+          <t>-32,53; 11,24</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 33,26</t>
+          <t>-7,72; 32,11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,88; 40,32</t>
+          <t>2,71; 40,1</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 27,46</t>
+          <t>-12,46; 25,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8,91; 48,48</t>
+          <t>8,6; 46,43</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 10,89</t>
+          <t>-1,71; 10,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 11,51</t>
+          <t>-1,02; 11,12</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,03; 19,23</t>
+          <t>8,27; 19,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 7,27</t>
+          <t>-3,24; 7,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 7,84</t>
+          <t>-2,43; 8,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,12; 14,95</t>
+          <t>4,28; 14,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 7,42</t>
+          <t>-0,56; 7,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,17; 7,87</t>
+          <t>0,22; 8,6</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8,12; 16,0</t>
+          <t>7,8; 15,7</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 17,01</t>
+          <t>-2,21; 15,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 18,22</t>
+          <t>-1,43; 17,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10,89; 29,98</t>
+          <t>11,88; 31,74</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 10,59</t>
+          <t>-4,31; 10,62</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 11,37</t>
+          <t>-3,21; 11,98</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,51; 21,52</t>
+          <t>5,73; 21,13</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 10,72</t>
+          <t>-0,79; 11,16</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,24; 11,62</t>
+          <t>0,29; 12,57</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11,34; 23,9</t>
+          <t>10,83; 23,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 9,49</t>
+          <t>-18,57; 10,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 14,56</t>
+          <t>-16,81; 14,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 13,54</t>
+          <t>-12,68; 13,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 12,1</t>
+          <t>-15,24; 12,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 1,12</t>
+          <t>-26,15; 1,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 19,17</t>
+          <t>-3,0; 20,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 8,0</t>
+          <t>-13,03; 7,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 4,09</t>
+          <t>-17,18; 3,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 13,53</t>
+          <t>-4,85; 12,9</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 13,88</t>
+          <t>-23,39; 16,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 20,96</t>
+          <t>-21,18; 19,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 20,11</t>
+          <t>-15,36; 20,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 16,49</t>
+          <t>-17,89; 17,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 1,58</t>
+          <t>-31,43; 1,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 27,5</t>
+          <t>-3,5; 30,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 10,93</t>
+          <t>-16,13; 10,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 5,71</t>
+          <t>-20,93; 5,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 19,09</t>
+          <t>-5,81; 18,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 23,81</t>
+          <t>-8,49; 22,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 29,32</t>
+          <t>-1,11; 27,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 31,09</t>
+          <t>2,66; 30,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 24,59</t>
+          <t>-6,74; 23,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 27,32</t>
+          <t>-3,58; 26,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 35,03</t>
+          <t>7,67; 35,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 19,07</t>
+          <t>-3,98; 18,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 23,11</t>
+          <t>1,55; 22,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 28,3</t>
+          <t>8,58; 29,01</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 43,36</t>
+          <t>-11,34; 41,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 53,69</t>
+          <t>-0,8; 50,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 57,18</t>
+          <t>3,68; 54,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 44,87</t>
+          <t>-9,12; 39,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 47,36</t>
+          <t>-4,76; 47,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 63,66</t>
+          <t>10,41; 64,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 32,46</t>
+          <t>-5,54; 30,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 39,08</t>
+          <t>2,11; 37,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,28; 48,49</t>
+          <t>11,85; 48,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 26,89</t>
+          <t>-5,33; 26,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 26,55</t>
+          <t>-6,35; 28,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 25,59</t>
+          <t>-9,91; 26,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 16,34</t>
+          <t>-14,53; 15,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 25,21</t>
+          <t>-3,09; 24,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 12,17</t>
+          <t>-22,07; 13,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 15,33</t>
+          <t>-4,72; 16,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 20,71</t>
+          <t>-0,74; 20,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 14,3</t>
+          <t>-12,28; 13,57</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 48,09</t>
+          <t>-6,49; 47,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 45,95</t>
+          <t>-7,49; 52,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 45,91</t>
+          <t>-12,9; 47,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 25,38</t>
+          <t>-18,72; 22,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 39,34</t>
+          <t>-3,96; 37,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,69; 18,9</t>
+          <t>-28,66; 21,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 23,76</t>
+          <t>-6,1; 25,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 33,07</t>
+          <t>-0,47; 32,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 22,17</t>
+          <t>-16,3; 20,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 9,47</t>
+          <t>-10,44; 11,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 8,11</t>
+          <t>-10,64; 9,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 22,5</t>
+          <t>3,2; 21,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 14,5</t>
+          <t>-6,1; 13,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 12,53</t>
+          <t>-7,21; 12,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 11,73</t>
+          <t>-9,98; 12,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 9,33</t>
+          <t>-4,62; 9,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 8,2</t>
+          <t>-6,39; 7,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 14,03</t>
+          <t>-0,68; 13,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 14,46</t>
+          <t>-13,54; 16,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 12,07</t>
+          <t>-14,3; 14,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,22; 34,81</t>
+          <t>4,36; 32,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 21,81</t>
+          <t>-7,71; 19,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 18,96</t>
+          <t>-9,16; 18,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 17,55</t>
+          <t>-12,9; 17,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 13,51</t>
+          <t>-6,16; 13,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 11,93</t>
+          <t>-8,43; 10,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 20,72</t>
+          <t>-0,88; 20,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 23,72</t>
+          <t>-6,53; 23,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 22,65</t>
+          <t>-6,48; 22,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,41; 38,31</t>
+          <t>6,58; 37,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 11,27</t>
+          <t>-15,37; 10,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 24,08</t>
+          <t>0,28; 23,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,57; 30,62</t>
+          <t>6,43; 30,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 12,02</t>
+          <t>-6,72; 12,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 17,7</t>
+          <t>-0,03; 18,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,06; 31,1</t>
+          <t>12,28; 31,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 52,75</t>
+          <t>-9,91; 52,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 49,61</t>
+          <t>-9,89; 49,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10,58; 83,75</t>
+          <t>12,11; 84,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 18,45</t>
+          <t>-20,47; 17,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 39,95</t>
+          <t>0,37; 37,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,33; 51,7</t>
+          <t>8,93; 50,53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 20,94</t>
+          <t>-10,04; 21,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 31,18</t>
+          <t>0,04; 33,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17,04; 55,3</t>
+          <t>18,78; 56,33</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 35,51</t>
+          <t>1,57; 36,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 31,83</t>
+          <t>-0,66; 31,88</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,98; 40,2</t>
+          <t>8,6; 38,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 20,4</t>
+          <t>-10,02; 20,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 7,94</t>
+          <t>-27,05; 9,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 21,84</t>
+          <t>-7,6; 23,2</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,17; 24,51</t>
+          <t>0,84; 24,27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 16,37</t>
+          <t>-9,21; 16,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,43; 28,21</t>
+          <t>6,41; 27,88</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,05; 73,13</t>
+          <t>3,27; 74,46</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 62,08</t>
+          <t>-0,98; 62,21</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12,91; 83,54</t>
+          <t>12,83; 79,33</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 29,44</t>
+          <t>-12,02; 29,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 11,24</t>
+          <t>-32,06; 12,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 32,11</t>
+          <t>-8,73; 34,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,71; 40,1</t>
+          <t>1,15; 40,37</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 25,89</t>
+          <t>-12,26; 27,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8,6; 46,43</t>
+          <t>8,15; 45,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 10,07</t>
+          <t>-1,5; 10,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 11,12</t>
+          <t>-0,8; 10,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,27; 19,97</t>
+          <t>8,15; 19,62</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 7,44</t>
+          <t>-3,22; 7,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 8,29</t>
+          <t>-2,2; 8,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,67</t>
+          <t>4,33; 14,64</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 7,55</t>
+          <t>-1,07; 7,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,22; 8,6</t>
+          <t>0,24; 8,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,8; 15,7</t>
+          <t>8,12; 15,67</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 15,46</t>
+          <t>-2,13; 15,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 17,57</t>
+          <t>-1,15; 16,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11,88; 31,74</t>
+          <t>11,67; 31,12</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 10,62</t>
+          <t>-4,32; 11,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 11,98</t>
+          <t>-2,87; 11,97</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,73; 21,13</t>
+          <t>5,34; 20,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 11,16</t>
+          <t>-1,49; 10,71</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,29; 12,57</t>
+          <t>0,42; 12,17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10,83; 23,27</t>
+          <t>11,34; 23,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-12,17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,59</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-3,41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-12,17</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,21</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,31</t>
+          <t>3,38</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 10,96</t>
+          <t>-14,98; 12,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 14,07</t>
+          <t>-26,12; 3,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 13,91</t>
+          <t>-4,87; 17,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 12,29</t>
+          <t>-19,6; 10,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 1,12</t>
+          <t>-18,29; 13,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 20,66</t>
+          <t>-14,3; 12,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 7,63</t>
+          <t>-13,08; 7,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 3,7</t>
+          <t>-17,45; 4,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 12,9</t>
+          <t>-5,14; 13,39</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-1,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-15,4%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-4,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-0,68%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,34%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-15,4%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>-1,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 16,25</t>
+          <t>-17,75; 16,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 19,95</t>
+          <t>-31,32; 4,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 20,46</t>
+          <t>-5,49; 25,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 17,59</t>
+          <t>-23,42; 15,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 1,41</t>
+          <t>-21,76; 20,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 30,81</t>
+          <t>-17,79; 18,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 10,12</t>
+          <t>-16,5; 10,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 5,2</t>
+          <t>-21,44; 6,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 18,19</t>
+          <t>-6,22; 18,48</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,72</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21,06</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,47</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,39</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,21</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,72</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,49</t>
+          <t>16,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18,54</t>
+          <t>18,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 22,64</t>
+          <t>-8,1; 24,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 27,98</t>
+          <t>-5,13; 25,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 30,74</t>
+          <t>6,52; 35,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 23,39</t>
+          <t>-8,5; 23,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 26,83</t>
+          <t>-0,86; 29,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 35,54</t>
+          <t>0,94; 30,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 18,76</t>
+          <t>-4,91; 17,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 22,8</t>
+          <t>1,44; 22,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 29,01</t>
+          <t>8,67; 28,7</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>9,62%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>19,91%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24,28%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 41,23</t>
+          <t>-10,84; 43,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 50,2</t>
+          <t>-6,79; 45,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 54,91</t>
+          <t>8,68; 64,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 39,4</t>
+          <t>-11,16; 39,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 47,37</t>
+          <t>-0,8; 54,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 64,81</t>
+          <t>1,19; 54,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 30,92</t>
+          <t>-6,66; 29,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 37,96</t>
+          <t>1,81; 38,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 48,22</t>
+          <t>11,56; 49,41</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,97</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,18</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,3</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>10,54</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>10,41</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,42</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,18</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,09</t>
+          <t>9,17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>2,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 26,25</t>
+          <t>-13,6; 15,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 28,71</t>
+          <t>-2,31; 26,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 26,9</t>
+          <t>-20,5; 13,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 15,32</t>
+          <t>-5,72; 24,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 24,4</t>
+          <t>-7,43; 27,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 13,4</t>
+          <t>-9,77; 27,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 16,48</t>
+          <t>-5,54; 16,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 20,91</t>
+          <t>-0,21; 22,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 13,57</t>
+          <t>-10,6; 14,64</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-3,19%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>15,65%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>15,46%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,66%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 47,34</t>
+          <t>-17,47; 23,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 52,19</t>
+          <t>-2,8; 42,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 47,25</t>
+          <t>-26,16; 20,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 22,88</t>
+          <t>-7,33; 43,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 37,72</t>
+          <t>-10,0; 49,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 21,18</t>
+          <t>-13,46; 47,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 25,41</t>
+          <t>-7,25; 26,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 32,94</t>
+          <t>-0,01; 35,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 20,71</t>
+          <t>-14,43; 22,42</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,98</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,08</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,03</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13,19</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,98</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>11,98</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>6,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 11,16</t>
+          <t>-5,83; 14,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 9,38</t>
+          <t>-7,6; 12,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,2; 21,91</t>
+          <t>-9,13; 12,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 13,32</t>
+          <t>-11,65; 10,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 12,44</t>
+          <t>-11,79; 9,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 12,22</t>
+          <t>2,03; 21,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 9,19</t>
+          <t>-5,63; 9,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 7,43</t>
+          <t>-7,13; 7,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 13,99</t>
+          <t>-0,16; 14,32</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-0,04%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-2,09%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18,3%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 16,72</t>
+          <t>-7,85; 20,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 14,29</t>
+          <t>-9,91; 18,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,36; 32,93</t>
+          <t>-11,58; 18,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 19,3</t>
+          <t>-15,08; 15,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 18,63</t>
+          <t>-15,16; 13,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 17,91</t>
+          <t>2,84; 33,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 13,18</t>
+          <t>-7,42; 13,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 10,85</t>
+          <t>-9,36; 10,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 20,45</t>
+          <t>-0,16; 21,24</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,61</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10,94</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19,01</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>8,88</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>8,07</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>23,42</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10,94</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,64</t>
+          <t>26,84</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21,63</t>
+          <t>22,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 23,91</t>
+          <t>-14,5; 12,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 22,8</t>
+          <t>-1,34; 24,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,58; 37,95</t>
+          <t>7,22; 31,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 10,66</t>
+          <t>-4,95; 23,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 23,05</t>
+          <t>-6,51; 22,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,43; 30,16</t>
+          <t>12,34; 40,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 12,13</t>
+          <t>-7,02; 12,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 18,55</t>
+          <t>0,27; 18,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,28; 31,57</t>
+          <t>14,38; 31,07</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-2,36%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>16,08%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>27,95%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>15,93%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>14,47%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>42,01%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-2,36%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>16,08%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 52,1</t>
+          <t>-19,76; 20,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 49,98</t>
+          <t>-1,79; 40,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12,11; 84,21</t>
+          <t>10,36; 52,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 17,58</t>
+          <t>-7,9; 50,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,37; 37,55</t>
+          <t>-9,77; 51,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,93; 50,53</t>
+          <t>19,64; 88,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 21,29</t>
+          <t>-10,39; 21,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,04; 33,52</t>
+          <t>0,09; 31,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18,78; 56,33</t>
+          <t>21,42; 54,67</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>5,54</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-8,95</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8,3</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>19,11</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>16,5</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>25,06</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5,54</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-8,95</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>25,33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17,18</t>
+          <t>17,3</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,57; 36,88</t>
+          <t>-9,32; 19,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 31,88</t>
+          <t>-26,61; 7,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,6; 38,91</t>
+          <t>-7,66; 23,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 20,0</t>
+          <t>0,53; 35,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 9,66</t>
+          <t>-2,46; 33,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 23,2</t>
+          <t>8,3; 40,17</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,84; 24,27</t>
+          <t>2,09; 24,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 16,55</t>
+          <t>-8,3; 16,93</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,41; 27,88</t>
+          <t>6,29; 28,94</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-11,48%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>31,89%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>27,54%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>41,82%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-11,48%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3,27; 74,46</t>
+          <t>-10,74; 28,58</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 62,21</t>
+          <t>-31,78; 10,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12,83; 79,33</t>
+          <t>-8,5; 33,62</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 29,47</t>
+          <t>0,69; 70,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 12,77</t>
+          <t>-2,97; 68,66</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 34,72</t>
+          <t>12,17; 82,35</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,15; 40,37</t>
+          <t>2,88; 40,32</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 27,12</t>
+          <t>-11,36; 27,46</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8,15; 45,58</t>
+          <t>9,02; 48,43</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2,19</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2,98</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>9,73</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>4,47</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>5,29</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>14,07</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2,98</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>14,25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11,81</t>
+          <t>11,95</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 10,1</t>
+          <t>-3,51; 7,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 10,88</t>
+          <t>-2,37; 7,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,15; 19,62</t>
+          <t>4,19; 14,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 7,84</t>
+          <t>-1,04; 10,89</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 8,32</t>
+          <t>-0,3; 11,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,33; 14,64</t>
+          <t>7,87; 19,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 7,23</t>
+          <t>-0,73; 7,42</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,24; 8,2</t>
+          <t>0,17; 7,87</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8,12; 15,67</t>
+          <t>8,37; 16,11</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>6,63%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>7,86%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>20,88%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 15,34</t>
+          <t>-4,54; 10,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 16,89</t>
+          <t>-3,16; 11,37</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11,67; 31,12</t>
+          <t>5,58; 21,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 11,37</t>
+          <t>-1,6; 17,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 11,97</t>
+          <t>-0,33; 18,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,34; 20,93</t>
+          <t>11,04; 29,92</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 10,71</t>
+          <t>-1,05; 10,72</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,42; 12,17</t>
+          <t>0,24; 11,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11,34; 23,03</t>
+          <t>11,56; 23,81</t>
         </is>
       </c>
     </row>
